--- a/stories/arbres/ATOM-REL.CON.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux. Hermine dit : stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hermine marche vers la maîtresse. Elle dit : on m'a bousculée. La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte. Maman dit : tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
+          <t>Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hermine marche vers la maîtresse. On m'a bousculée. La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux.
+enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
+narrateur|Hermine marche vers la maîtresse.
+narrateur|On m'a bousculée.
+narrateur|La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte.
+maman|Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.
+narrateur|Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Hermine. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hermine a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend la main d'Hermine. Elles marchent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Un camarade bouscule Hermine. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Hermine a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Maman prend la main d'Hermine. Elles marchent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hermine dit stop à l'école</t>
+          <t>Nina dit stop près des manteaux</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina range les manteaux sous le préau. Un camarade bouscule la file. Nina dit stop, s'éloigne, rejoint la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux. Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hermine marche vers la maîtresse. On m'a bousculée. La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
+          <t>Les manteaux mouillés fument un peu. La laine sent le chaud et l'eau. Une petite vapeur monte, puis plus. Un crochet de métal tinte. Une capuche rouge pend, toute lourde. Une goutte tombe de la capuche. Maman aide Nina avec la manche. Ta manche est rentrée, Nina ? Oui, maman. Elle était collée. C'est la pluie. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Nina est sous le préau. Elle est dans la file des manteaux. Ses chaussettes sont un peu froides. Ma capuche est lourde. Nina cherche son crochet. Le crochet est froid sous le doigt. La capuche pend, enfin. Un camarade arrive trop vite. Il bouscule la file des manteaux. Nina sent son épaule. Son cœur tape. Stop. Nina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Nina marche vers la porte. Le crochet tinte encore. On m'a bousculée. La maîtresse l'écoute. Nina reste près d'elle. Elle pose une main sur la porte. La porte est lisse et froide. Je reste ici. La capuche rouge ne bouge plus. Nina souffle. Son cœur tape moins vite. Le soir, maman revient. Les manteaux ont séché un peu. Nina touche sa capuche. Elle est moins lourde. Tu as rangé ta capuche ? Oui. Un camarade trop près. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Ta manche est sèche, maintenant ? Un peu. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Nina hoche la tête. Elle sent la main de maman. La main est chaude.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux.
-enfant-f|Stop. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse.
-narrateur|Hermine marche vers la maîtresse.
-narrateur|On m'a bousculée.
-narrateur|La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte.
-maman|Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse.
-narrateur|Hermine hoche la tête. Elle sent la main de maman. La main est chaude.</t>
+          <t>narrateur|Les manteaux mouillés fument un peu.
+narrateur|La laine sent le chaud et l'eau.
+narrateur|Une petite vapeur monte, puis plus.
+narrateur|Un crochet de métal tinte.
+narrateur|Une capuche rouge pend, toute lourde.
+narrateur|Une goutte tombe de la capuche.
+narrateur|Maman aide Nina avec la manche.
+maman|Ta manche est rentrée, Nina ?
+enfant-f|Oui, maman.
+enfant-f|Elle était collée.
+maman|C'est la pluie.
+maman|Je reviens ce soir.
+enfant-f|D'accord.
+narrateur|La maîtresse est près de la porte.
+narrateur|En ce moment, Nina est sous le préau.
+narrateur|Elle est dans la file des manteaux.
+narrateur|Ses chaussettes sont un peu froides.
+enfant-f|Ma capuche est lourde.
+narrateur|Nina cherche son crochet.
+narrateur|Le crochet est froid sous le doigt.
+narrateur|La capuche pend, enfin.
+narrateur|Un camarade arrive trop vite.
+narrateur|Il bouscule la file des manteaux.
+narrateur|Nina sent son épaule.
+narrateur|Son cœur tape.
+enfant-f|Stop.
+narrateur|Nina fait un pas.
+narrateur|Elle peut s'éloigner.
+narrateur|S'éloigner, c'est aller vers la maîtresse.
+narrateur|Nina marche vers la porte.
+narrateur|Le crochet tinte encore.
+enfant-f|On m'a bousculée.
+narrateur|La maîtresse l'écoute.
+narrateur|Nina reste près d'elle.
+narrateur|Elle pose une main sur la porte.
+narrateur|La porte est lisse et froide.
+enfant-f|Je reste ici.
+narrateur|La capuche rouge ne bouge plus.
+narrateur|Nina souffle.
+narrateur|Son cœur tape moins vite.
+narrateur|Le soir, maman revient.
+narrateur|Les manteaux ont séché un peu.
+narrateur|Nina touche sa capuche.
+narrateur|Elle est moins lourde.
+maman|Tu as rangé ta capuche ?
+enfant-f|Oui.
+enfant-f|Un camarade trop près.
+enfant-f|J'ai dit stop.
+enfant-f|Je suis allée vers la maîtresse.
+maman|Bravo, Nina.
+maman|Tu as dit stop.
+maman|Tu t'es éloignée.
+maman|Tu es allée vers la maîtresse.
+maman|C'est du bon travail.
+maman|Ta manche est sèche, maintenant ?
+enfant-f|Un peu.
+maman|Et toi, tu as su quoi faire.
+enfant-f|Stop.
+enfant-f|Puis la maîtresse.
+narrateur|Nina hoche la tête.
+narrateur|Elle sent la main de maman.
+narrateur|La main est chaude.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Hermine. Que fait-elle ?</t>
+          <t>Un camarade bouscule Nina. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Hermine. Que fait-elle ?</t>
+          <t>narrateur|Un camarade bouscule Nina.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hermine a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse.</t>
+          <t>Nina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1742,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hermine a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse.</t>
+          <t>narrateur|Nina a dit stop.
+narrateur|Elle s'est éloignée.
+narrateur|Elle a rejoint la maîtresse.
+maman|Bravo.
+maman|C'est le bon geste.
+enfant-f|Stop, puis la maîtresse.
+maman|Oui.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend la main d'Hermine. Elles marchent.</t>
+          <t>Maman prend la main de Nina. On marche ? Oui, maman. Le crochet de métal ne tinte plus. Ta capuche est moins lourde ? Oui. Ta manche est rentrée ? Oui, maman. Les manteaux restent en rang, tout calmes. La petite vapeur n'est plus là. On laisse la capuche au crochet ? Oui. Une goutte a séché sur le sol.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1917,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend la main d'Hermine. Elles marchent.</t>
+          <t>narrateur|Maman prend la main de Nina.
+maman|On marche ?
+enfant-f|Oui, maman.
+narrateur|Le crochet de métal ne tinte plus.
+maman|Ta capuche est moins lourde ?
+enfant-f|Oui.
+maman|Ta manche est rentrée ?
+enfant-f|Oui, maman.
+narrateur|Les manteaux restent en rang, tout calmes.
+narrateur|La petite vapeur n'est plus là.
+maman|On laisse la capuche au crochet ?
+enfant-f|Oui.
+narrateur|Une goutte a séché sur le sol.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as fait du bon travail. La laine ne fume plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2097,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit stop.
+enfant-f|Je suis allée vers la maîtresse.
+maman|Bravo, Nina.
+maman|Tu as fait du bon travail.
+narrateur|La laine ne fume plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2162,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les manteaux mouillés fument un peu. La laine sent le chaud et l'eau. Une petite vapeur monte, puis plus. Un crochet de métal tinte. Une capuche rouge pend, toute lourde. Une goutte tombe de la capuche. Maman aide Nina avec la manche. Ta manche est rentrée, Nina ? Oui, maman. Elle était collée. C'est la pluie. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Nina est sous le préau. Elle est dans la file des manteaux. Ses chaussettes sont un peu froides. Ma capuche est lourde. Nina cherche son crochet. Le crochet est froid sous le doigt. La capuche pend, enfin. Un camarade arrive trop vite. Il bouscule la file des manteaux. Nina sent son épaule. Son cœur tape. Stop. Nina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Nina marche vers la porte. Le crochet tinte encore. On m'a bousculée. La maîtresse l'écoute. Nina reste près d'elle. Elle pose une main sur la porte. La porte est lisse et froide. Je reste ici. La capuche rouge ne bouge plus. Nina souffle. Son cœur tape moins vite. Le soir, maman revient. Les manteaux ont séché un peu. Nina touche sa capuche. Elle est moins lourde. Tu as rangé ta capuche ? Oui. Un camarade trop près. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. C'est du bon travail. Ta manche est sèche, maintenant ? Un peu. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Nina hoche la tête. Elle sent la main de maman. La main est chaude.</t>
+          <t>Les manteaux mouillés fument un peu. La laine sent le chaud et l'eau. Une petite vapeur monte, puis plus. Un crochet de métal tinte. Une capuche rouge pend, toute lourde. Une goutte tombe de la capuche. Maman aide Nina avec la manche. Ta manche est rentrée, Nina ? Oui, maman. Elle était collée. C'est la pluie. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Nina est sous le préau. Elle est dans la file des manteaux. Ses chaussettes sont un peu froides. Ma capuche est lourde. Nina cherche son crochet. Le crochet est froid sous le doigt. La capuche pend, enfin. Un camarade arrive trop vite. Il bouscule la file des manteaux. Nina sent son épaule. Son cœur tape. Stop. Nina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Nina marche vers la porte. Le crochet tinte encore. On m'a bousculée. La maîtresse l'écoute. Nina reste près d'elle. Elle pose une main sur la porte. La porte est lisse et froide. Je reste ici. La capuche rouge ne bouge plus. Nina souffle. Son cœur tape moins vite. Le soir, maman revient. Les manteaux ont séché un peu. Nina touche sa capuche. Elle est moins lourde. Tu as rangé ta capuche ? Oui. Un camarade trop près. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Ta manche est sèche, maintenant ? Un peu. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Nina hoche la tête. Elle sent la main de maman. La main est chaude.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hermine est sous le préau. La maîtresse est près de la porte. Un camarade bouscule la file des manteaux. Hermine dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle fait un pas. Elle doit s'éloigner. S'éloigner, c'est aller vers la maîtresse. Hermine marche vers la maîtresse. Elle dit : on m'a bousculée. La maîtresse l'écoute. Hermine reste près d'elle. Le soir, maman vient. Hermine raconte. Maman dit : tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Hermine hoche la tête. Elle sent la main de maman. La main est chaude.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les manteaux mouillés fument un peu. La laine sent le chaud et l'eau. Une petite vapeur monte, puis plus. Un crochet de métal tinte. Une capuche rouge pend, toute lourde. Une goutte tombe de la capuche. Maman aide Nina avec la manche. Ta manche est rentrée, Nina ? Oui, maman. Elle était collée. C'est la pluie. Je reviens ce soir. D'accord. La maîtresse est près de la porte. En ce moment, Nina est sous le préau. Elle est dans la file des manteaux. Ses chaussettes sont un peu froides. Ma capuche est lourde. Nina cherche son crochet. Le crochet est froid sous le doigt. La capuche pend, enfin. Un camarade arrive trop vite. Il bouscule la file des manteaux. Nina sent son épaule. Son cœur tape. Stop. Nina fait un pas. Elle peut s'éloigner. S'éloigner, c'est aller vers la maîtresse. Nina marche vers la porte. Le crochet tinte encore. On m'a bousculée. La maîtresse l'écoute. Nina reste près d'elle. Elle pose une main sur la porte. La porte est lisse et froide. Je reste ici. La capuche rouge ne bouge plus. Nina souffle. Son cœur tape moins vite. Le soir, maman revient. Les manteaux ont séché un peu. Nina touche sa capuche. Elle est moins lourde. Tu as rangé ta capuche ? Oui. Un camarade trop près. J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as dit stop. Tu t'es éloignée. Tu es allée vers la maîtresse. Ta manche est sèche, maintenant ? Un peu. Et toi, tu as su quoi faire. Stop. Puis la maîtresse. Nina hoche la tête. Elle sent la main de maman. La main est chaude.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1377,7 +1377,6 @@
 maman|Tu as dit stop.
 maman|Tu t'es éloignée.
 maman|Tu es allée vers la maîtresse.
-maman|C'est du bon travail.
 maman|Ta manche est sèche, maintenant ?
 enfant-f|Un peu.
 maman|Et toi, tu as su quoi faire.
@@ -1388,7 +1387,6 @@
 narrateur|La main est chaude.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1418,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Un camarade bouscule Hermine. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Nina. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1571,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,12 +1595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop, puis la maîtresse. Oui. Tu as fait du bon travail.</t>
+          <t>Nina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hermine a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Elle s'est éloignée. Elle a rejoint la maîtresse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a dit stop. Elle s'est éloignée. Elle a rejoint la maîtresse. Bravo. C'est le bon geste. Stop, puis la maîtresse. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,11 +1745,9 @@
 maman|Bravo.
 maman|C'est le bon geste.
 enfant-f|Stop, puis la maîtresse.
-maman|Oui.
-maman|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; d'Hermine. Elles marchent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman prend la main de Nina. On marche ? Oui, maman. Le crochet de métal ne tinte plus. Ta capuche est moins lourde ? Oui. Ta manche est rentrée ? Oui, maman. Les manteaux restent en rang, tout calmes. La petite vapeur n'est plus là. On laisse la capuche au crochet ? Oui. Une goutte a séché sur le sol.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1927,6 @@
 narrateur|Une goutte a séché sur le sol.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. Tu as fait du bon travail. La laine ne fume plus. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. La laine ne fume plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis allée vers la maîtresse. Bravo, Nina. La laine ne fume plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,12 +2094,9 @@
           <t>enfant-f|J'ai dit stop.
 enfant-f|Je suis allée vers la maîtresse.
 maman|Bravo, Nina.
-maman|Tu as fait du bon travail.
-narrateur|La laine ne fume plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La laine ne fume plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.002-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école</t>
+          <t>école, préau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hermine, maîtresse, maman</t>
+          <t>Nina, maîtresse, maman</t>
         </is>
       </c>
     </row>
